--- a/data/trans_orig/IP04D$notiene-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130736</t>
+          <t>130718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137643</t>
+          <t>137622</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>140520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151090</t>
+          <t>150914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275407</t>
+          <t>275510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287174</t>
+          <t>286865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19773</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192587</t>
+          <t>192946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201298</t>
+          <t>201288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212856</t>
+          <t>212638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221037</t>
+          <t>220904</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409081</t>
+          <t>409913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>420721</t>
+          <t>420731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16188</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14466</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>27039</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139188</t>
+          <t>139711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148991</t>
+          <t>149334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>150844</t>
+          <t>150908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160490</t>
+          <t>160605</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293369</t>
+          <t>293647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>307830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25265</t>
+          <t>26151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193458</t>
+          <t>194723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>205193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193200</t>
+          <t>192956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204175</t>
+          <t>204018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392641</t>
+          <t>391755</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407977</t>
+          <t>407168</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74764</t>
+          <t>72732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>669146</t>
+          <t>670325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>686963</t>
+          <t>687544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711206</t>
+          <t>710143</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>729919</t>
+          <t>730041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385753</t>
+          <t>1387785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412623</t>
+          <t>1413458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12877</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38060</t>
+          <t>36780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58302</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>106851</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119995</t>
+          <t>120221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110594</t>
+          <t>110388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127256</t>
+          <t>127765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222646</t>
+          <t>221840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242888</t>
+          <t>244168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19665</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41973</t>
+          <t>41614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>47121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171126</t>
+          <t>171142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186314</t>
+          <t>186522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181715</t>
+          <t>182074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199124</t>
+          <t>199265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358868</t>
+          <t>358728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381339</t>
+          <t>382546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>31910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>27078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49349</t>
+          <t>50099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>72914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123647</t>
+          <t>124087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>137538</t>
+          <t>137215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121597</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138659</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>250032</t>
+          <t>248997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>272562</t>
+          <t>271812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29637</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175695</t>
+          <t>176680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>190248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179839</t>
+          <t>180754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192552</t>
+          <t>192545</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360808</t>
+          <t>361197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380105</t>
+          <t>380993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107958</t>
+          <t>105936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95798</t>
+          <t>96101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131128</t>
+          <t>128502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>181435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228599</t>
+          <t>227202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>592223</t>
+          <t>594245</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>622041</t>
+          <t>620618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608883</t>
+          <t>611509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>644213</t>
+          <t>643910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1211593</t>
+          <t>1212990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257879</t>
+          <t>1258757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>31995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40489</t>
+          <t>37349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105092</t>
+          <t>104671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114048</t>
+          <t>113753</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>108417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136232</t>
+          <t>136310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217204</t>
+          <t>220344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>248028</t>
+          <t>247524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>47111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>19098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42239</t>
+          <t>42542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76427</t>
+          <t>77487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143698</t>
+          <t>142402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170259</t>
+          <t>170540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216534</t>
+          <t>217724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235249</t>
+          <t>235230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367414</t>
+          <t>366354</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>401299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>54483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34842</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60262</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63936</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105024</t>
+          <t>105776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136736</t>
+          <t>135918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166079</t>
+          <t>165545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125024</t>
+          <t>125153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>150444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270663</t>
+          <t>269911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311751</t>
+          <t>310484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>31914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146647</t>
+          <t>147009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158408</t>
+          <t>158195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149304</t>
+          <t>148381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167629</t>
+          <t>167040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>301111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322008</t>
+          <t>321567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>71831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110824</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86163</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130400</t>
+          <t>128326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168093</t>
+          <t>168616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229820</t>
+          <t>228630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554332</t>
+          <t>553319</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>592211</t>
+          <t>593325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>629922</t>
+          <t>631996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674159</t>
+          <t>674409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195657</t>
+          <t>1196847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1257384</t>
+          <t>1256861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$notiene-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$notiene-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14142</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3107</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7670</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7446</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3770</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14164</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147238</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140542</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>151107</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135281</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130718</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137622</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130490</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137636</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147238</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140520</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>150914</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>275510</t>
+          <t>274762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286865</t>
+          <t>286959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11299</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6841</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12073</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3467</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11426</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5951</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11197</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>217884</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>212536</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221271</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>198178</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>192946</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>201288</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>193593</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>201552</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>217884</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>212638</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>220904</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409913</t>
+          <t>410057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>420731</t>
+          <t>421084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4839</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14729</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10497</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15665</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6496</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16840</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8757</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4705</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14402</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156553</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>150581</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160471</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>144879</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>139711</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>149334</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138536</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>148880</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156553</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>150908</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160605</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293647</t>
+          <t>293953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307830</t>
+          <t>307542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14913</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>8476</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4317</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14787</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15785</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8383</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4378</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15440</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>25365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>200013</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>193483</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204319</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>201034</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>194723</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>205193</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>193725</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>205493</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>200013</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>192956</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>204018</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391755</t>
+          <t>392541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407168</t>
+          <t>407566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22281</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>41389</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20748</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37967</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21305</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39198</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22184</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42082</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>721688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>710836</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>729944</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>980</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679370</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670325</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>687544</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>669094</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>686987</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>721688</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>710143</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>730041</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1387785</t>
+          <t>1387472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413458</t>
+          <t>1412597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,74 +2669,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28285</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20833</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37611</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>19044</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12651</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26021</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12495</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26013</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>19,58%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28285</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20311</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37688</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36780</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59108</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -2787,67 +2787,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>119791</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>110465</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>127243</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>113828</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>106851</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>120221</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>106859</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>120377</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>85,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>80,42%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>119791</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>110388</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>127765</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221840</t>
+          <t>222094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>244168</t>
+          <t>243687</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32210</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23954</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42028</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26517</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19457</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34837</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20243</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35294</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>12,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32210</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24423</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41614</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47121</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>70189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>181660</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>199734</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>85,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>179462</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>171142</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>186522</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>170685</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>185736</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>87,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>182074</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>199265</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>85,6%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358728</t>
+          <t>359478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>382546</t>
+          <t>381580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35518</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26254</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44495</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25256</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18782</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31910</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18442</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32565</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>35518</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>27078</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>44092</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>49896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72914</t>
+          <t>71978</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121419</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139660</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>130741</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>124087</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>137215</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123432</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>137555</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130396</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121822</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138836</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>248997</t>
+          <t>249933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>271812</t>
+          <t>272015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15251</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9716</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22887</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21168</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15084</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28652</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14359</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>28349</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15251</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9788</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21579</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46468</t>
+          <t>47238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>179446</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>192617</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>184164</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>176680</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190248</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>176983</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190973</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>187082</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>180754</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>192545</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361197</t>
+          <t>360427</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380993</t>
+          <t>379276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>94773</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>129732</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>79563</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>105936</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>78028</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>106883</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>96101</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>128502</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181435</t>
+          <t>180428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>225587</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>628747</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>645238</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>608196</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>594245</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>620618</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>593298</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>622153</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>628747</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>611509</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>643910</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>84,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212990</t>
+          <t>1214605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1258757</t>
+          <t>1259764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3527</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12609</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37349</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119805</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114812</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123040</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>110594</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104671</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>113753</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>128961</t>
+          <t>114365</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108417</t>
+          <t>108495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136310</t>
+          <t>117420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>239556</t>
+          <t>234170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220344</t>
+          <t>227455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247524</t>
+          <t>239608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23842</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16068</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32878</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27945</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18973</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>47111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>14729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42542</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77487</t>
+          <t>56260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212748</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203712</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>220522</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>161568</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>142402</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>170540</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>227002</t>
+          <t>162755</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217724</t>
+          <t>153831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235230</t>
+          <t>168608</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>388570</t>
+          <t>375502</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366354</t>
+          <t>363667</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401299</t>
+          <t>385012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38839</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29851</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48953</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40180</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24856</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54483</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34842</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>42983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86450</t>
+          <t>73159</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65203</t>
+          <t>60056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105776</t>
+          <t>87050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129502</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>119388</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138490</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>150221</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135918</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>165545</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>78,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>139016</t>
+          <t>122730</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125153</t>
+          <t>114067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150444</t>
+          <t>130665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>289237</t>
+          <t>252232</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269911</t>
+          <t>238341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310484</t>
+          <t>265335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18857</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12337</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27459</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14883</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9767</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20953</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>33849</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>44482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149562</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140960</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>156082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>153079</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>147009</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>158195</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,18%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>159788</t>
+          <t>152153</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>148381</t>
+          <t>144989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>167040</t>
+          <t>157610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>312867</t>
+          <t>301715</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301111</t>
+          <t>291082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>321567</t>
+          <t>310595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73275</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>105461</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71831</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>111837</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128326</t>
+          <t>90782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168616</t>
+          <t>143231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228630</t>
+          <t>185929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>611616</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>593795</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>625981</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>825</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>575462</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>553319</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>593325</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,52%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>654768</t>
+          <t>552003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631996</t>
+          <t>537821</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674409</t>
+          <t>564514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1230229</t>
+          <t>1163619</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1196847</t>
+          <t>1141930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1256861</t>
+          <t>1184628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
